--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
@@ -108,10 +108,10 @@
     <t xml:space="preserve">Referent/Collecteur  (R/C)</t>
   </si>
   <si>
-    <t xml:space="preserve">date_debut (si R)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_fin (si R)</t>
+    <t xml:space="preserve">date_debut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_fin</t>
   </si>
   <si>
     <t xml:space="preserve">HOBO_n°02</t>
@@ -257,7 +257,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -300,12 +300,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -350,7 +344,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -376,10 +370,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1801,7 +1791,7 @@
       <c r="A81" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -1815,7 +1805,7 @@
       <c r="A82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -1827,7 +1817,7 @@
       <c r="A83" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -1841,7 +1831,7 @@
       <c r="A84" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C84" s="1" t="s">

--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Personnes&amp;Responsable_fichier" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Referent&amp;Collecteur_instrument" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Recolteur" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Groupe" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="76">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -108,10 +109,10 @@
     <t xml:space="preserve">Referent/Collecteur  (R/C)</t>
   </si>
   <si>
-    <t xml:space="preserve">date_debut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_fin</t>
+    <t xml:space="preserve">date_debut (si R)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_fin (si R)</t>
   </si>
   <si>
     <t xml:space="preserve">HOBO_n°02</t>
@@ -234,12 +235,6 @@
     <t xml:space="preserve">HOBO_n°38</t>
   </si>
   <si>
-    <t xml:space="preserve">TMS4_95224601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dendro_92261195</t>
-  </si>
-  <si>
     <t xml:space="preserve">description_recolteur</t>
   </si>
   <si>
@@ -247,6 +242,15 @@
   </si>
   <si>
     <t xml:space="preserve">Stagiaire n°02 qui doit compter les chiroptères</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nom_groupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mail_membre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3_BE_G1_2025_2026</t>
   </si>
 </sst>
 </file>
@@ -560,10 +564,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.9"/>
@@ -732,10 +737,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J85"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.38"/>
@@ -1788,55 +1794,15 @@
       <c r="D80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D81" s="6" t="n">
-        <v>45352</v>
-      </c>
+      <c r="D81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="D82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D83" s="6" t="n">
-        <v>45352</v>
-      </c>
+      <c r="D83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="D84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1923,10 +1889,6 @@
     <hyperlink ref="A78" r:id="rId77" display="marine.zwicke@umontpellier.fr"/>
     <hyperlink ref="A79" r:id="rId78" display="marine.zwicke@umontpellier.fr"/>
     <hyperlink ref="A80" r:id="rId79" display="marine.zwicke@umontpellier.fr"/>
-    <hyperlink ref="A81" r:id="rId80" display="marine.zwicke@umontpellier.fr"/>
-    <hyperlink ref="A82" r:id="rId81" display="marine.zwicke@umontpellier.fr"/>
-    <hyperlink ref="A83" r:id="rId82" display="marine.zwicke@umontpellier.fr"/>
-    <hyperlink ref="A84" r:id="rId83" display="marine.zwicke@umontpellier.fr"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1941,13 +1903,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1955,7 +1918,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C1" s="4"/>
     </row>
@@ -1964,7 +1927,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1972,7 +1935,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1988,4 +1951,48 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="guy.tare@etu.umontpellier.fr"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Personnes&amp;Responsable_fichier" sheetId="1" state="visible" r:id="rId3"/>
@@ -1917,7 +1917,7 @@
       <c r="A1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C1" s="4"/>
